--- a/Production/RepumperBoard/Split_Board.xlsx
+++ b/Production/RepumperBoard/Split_Board.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Augenblick/Documents/2025Summer/FreeCAD/Boards/PyOpticL_Rubidium_System/Production/RepumperBoard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kim/Desktop/Lab/Github/PyOpticL_Rubidium_System/Production/RepumperBoard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1828D101-C75B-3942-8716-36AA24CE90B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{64474019-B0B0-9140-93F3-5404B504BDAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2200" yWindow="2200" windowWidth="28040" windowHeight="17440" xr2:uid="{42F6A15E-87CE-9147-9545-45C46C70D310}"/>
+    <workbookView xWindow="14040" yWindow="740" windowWidth="15360" windowHeight="16680" xr2:uid="{42F6A15E-87CE-9147-9545-45C46C70D310}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,6 +27,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -52,9 +53,6 @@
     <t>Cube_Mount.step</t>
   </si>
   <si>
-    <t>KM05T</t>
-  </si>
-  <si>
     <t>M05</t>
   </si>
   <si>
@@ -113,6 +111,9 @@
   </si>
   <si>
     <t>Repumper Board</t>
+  </si>
+  <si>
+    <t>KA05T</t>
   </si>
 </sst>
 </file>
@@ -503,7 +504,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -516,7 +517,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -548,7 +549,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -556,7 +557,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -564,7 +565,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -572,7 +573,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -580,7 +581,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -588,7 +589,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>1</v>
@@ -596,7 +597,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15">
         <v>4</v>
@@ -604,7 +605,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16">
         <v>2</v>
@@ -612,7 +613,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -620,7 +621,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -628,7 +629,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B19">
         <v>2</v>
@@ -636,7 +637,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -644,7 +645,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -652,7 +653,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -660,7 +661,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -668,7 +669,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -676,7 +677,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -684,15 +685,15 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -702,8 +703,8 @@
   <hyperlinks>
     <hyperlink ref="A19" r:id="rId1" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=SM05L05" xr:uid="{26D03288-5EB5-E849-A9E7-78F166728512}"/>
     <hyperlink ref="A20" r:id="rId2" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=SM05FCA2" xr:uid="{7396B97A-1E53-F246-B983-DFB7235DDE2B}"/>
-    <hyperlink ref="A18" r:id="rId3" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=KM05T" xr:uid="{1BBCBD75-E5E4-9C42-9870-10D5AFE8751D}"/>
-    <hyperlink ref="A15" r:id="rId4" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=RSP05" xr:uid="{8DD89EFB-A6D7-DC45-81DC-A3DF706D2C18}"/>
+    <hyperlink ref="A18" r:id="rId3" xr:uid="{1BBCBD75-E5E4-9C42-9870-10D5AFE8751D}"/>
+    <hyperlink ref="A15" r:id="rId4" xr:uid="{8DD89EFB-A6D7-DC45-81DC-A3DF706D2C18}"/>
     <hyperlink ref="A21" r:id="rId5" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=BB05-E03" xr:uid="{A85C602C-A7C0-4B48-94F9-6B38884C0FD3}"/>
     <hyperlink ref="A22" r:id="rId6" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=S05TM09" xr:uid="{EF391373-8D5D-B54F-B9A3-5D87DFC3B5D2}"/>
     <hyperlink ref="A16" r:id="rId7" xr:uid="{103D64FF-9059-1B42-816A-F92B0274781E}"/>

--- a/Production/RepumperBoard/Split_Board.xlsx
+++ b/Production/RepumperBoard/Split_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kim/Desktop/Lab/Github/PyOpticL_Rubidium_System/Production/RepumperBoard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64474019-B0B0-9140-93F3-5404B504BDAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2FA3E6F-52E4-F748-A9C7-1733C166F6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14040" yWindow="740" windowWidth="15360" windowHeight="16680" xr2:uid="{42F6A15E-87CE-9147-9545-45C46C70D310}"/>
   </bookViews>
@@ -107,13 +107,13 @@
     <t>Surface_Adapter_aom.step</t>
   </si>
   <si>
-    <t>Split_Baseplate.step</t>
-  </si>
-  <si>
     <t>Repumper Board</t>
   </si>
   <si>
     <t>KA05T</t>
+  </si>
+  <si>
+    <t>Repumper_Baseplate.step</t>
   </si>
 </sst>
 </file>
@@ -504,7 +504,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -581,7 +581,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -621,7 +621,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18">
         <v>2</v>
